--- a/PMS/pms -unit testing.xlsx
+++ b/PMS/pms -unit testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Excel documents\PMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F026848-7575-48EF-ABF6-74CFB8B0BE6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D83F84-DBEC-4C60-9831-9F7CE76BF6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{9D7ECAA9-53A5-4B07-AA32-946F892554B9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9D7ECAA9-53A5-4B07-AA32-946F892554B9}"/>
   </bookViews>
   <sheets>
     <sheet name="PMS document " sheetId="1" r:id="rId1"/>
@@ -423,9 +423,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -434,6 +431,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1253,10 +1253,10 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="10"/>
+      <c r="B35" s="16"/>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
@@ -1390,18 +1390,18 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
-    <col min="2" max="2" width="89.1796875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="89.1796875" style="12" customWidth="1"/>
     <col min="3" max="3" width="19.54296875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       <c r="A3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
@@ -1426,10 +1426,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>54</v>
       </c>
       <c r="D4" t="s">
@@ -1437,10 +1437,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D5" t="s">
@@ -1448,10 +1448,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D6" t="s">
@@ -1459,10 +1459,10 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>56</v>
       </c>
       <c r="D7" t="s">
@@ -1470,10 +1470,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D9" t="s">
@@ -1481,10 +1481,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>58</v>
       </c>
       <c r="D10" t="s">
@@ -1495,7 +1495,7 @@
       <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>59</v>
       </c>
       <c r="D12" t="s">
@@ -1506,7 +1506,7 @@
       <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D13" t="s">
@@ -1517,7 +1517,7 @@
       <c r="A14" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>61</v>
       </c>
       <c r="D14" t="s">
@@ -1525,7 +1525,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>62</v>
       </c>
       <c r="D15" t="s">
@@ -1536,7 +1536,7 @@
       <c r="A17" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>63</v>
       </c>
       <c r="D17" t="s">
@@ -1547,7 +1547,7 @@
       <c r="A19" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>65</v>
       </c>
       <c r="D19" t="s">
@@ -1558,7 +1558,7 @@
       <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>66</v>
       </c>
       <c r="D20" t="s">
@@ -1569,7 +1569,7 @@
       <c r="A21" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D21" t="s">
@@ -1580,7 +1580,7 @@
       <c r="A23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D23" t="s">
